--- a/docs/project-proposal-v1.xlsx
+++ b/docs/project-proposal-v1.xlsx
@@ -19,140 +19,266 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <x:si>
     <x:t>① 공식 팬클럽 커뮤니에서 콘서트 정보를 알게됨 → ② 휠체어석을 예매하면 전담 스태프가 배치 → ③ 콘서트 장 입장 전부터 전담 스태프와 접견, 전담 스태프 도움으로 굿즈 구매 → ④ 전담 스태프가 입장, 관람, 퇴장까지 도움  → ⑤ 공연 후기를 네이버 카페에 남김 → ★ 남는 것: 그날 구매한 굿즈와 티켓</x:t>
   </x:si>
   <x:si>
+    <x:t>40대 초반 직장인, 서울 거주, 3년 전 사고로 복합장애를 얻어 수동휠체어를 사용, 한 아이돌 20년차 팬, 공식 팬클럽 가입, 음반/굿즈 수집, 장애를 얻기 전에는 콘서트, 팬미팅, 생일파티, 생일카페, 공개 방송과 같은 오프라인 스케줄에 자주 참여함. 장애인이 된 후로 오프라인 활동은 못하고 주말마다 스마트폰을 통해 공식 팬 커뮤니티, 네이버 카페로 소식을 얻고 팬활동을 함.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상영 중인  VR 콘서트를 찾아보니 휠체어석을 지원하지 않고 있어 VR 콘서트 감상 자체가 불가능하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.donga.com/news/Society/article/all/20260907/134619194/1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>① 페르소나가 구체적이라 생각해서 바꾸지 않음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질문 카드 (막힌 점·헷갈리는 점 한 가지 이상)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>★ 남은 «?» 개수  (어제 → 오늘)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v0  (어제 쓴 것 그대로)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현장 콘서트 티켓, 콘서트 굿즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>K-POP 이머시브 콘텐츠 기획자 양성과정 · 1기   ·   17일차 W4-2 (금)   ·   STUDIO 1 · 막힘 진단 → 기획안 v1 (★ D 고친 증거)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>①</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칸</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그대로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르소나가 구체적이라 생각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>★ 왜 바꿨나 — 한 줄</x:t>
+  </x:si>
+  <x:si>
+    <x:t>② Pain Point</x:t>
+  </x:si>
+  <x:si>
+    <x:t>③ 핵심 아이디어 한 줄</x:t>
+  </x:si>
+  <x:si>
+    <x:t>★ 안 바꾼 칸 + 그 이유</x:t>
+  </x:si>
+  <x:si>
     <x:t>극장은 콘서트장보다 사람이 덜 몰려 이동권 문제에 대한 두려움이 덜 할것이라 예상, 휠체어석 고정으로 인한 관람 제한 문제도 해결 가능함.</x:t>
   </x:si>
   <x:si>
-    <x:t>롯데 시네마 홈페이지에서 직접 확인: 현재 상영 중인 엔하이픈의 VR 콘서트 경우 롯데시네마 홍대입구 상영관 휠체어석은 예매불가이며 월드타워점은 휠체어석이 없는 전체 소파석이라 휠체어 사용자는 예매 자체가 불가능함</x:t>
+    <x:t>이동권 문제: 콘서트장 주변에 인파가 몰려 수동 휠체어를 타고 이동하기 어려울까봐 두렵다. (감정)</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve">페르소나와 유사한 사례
+</x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff1155cc"/>
+            <x:u/>
+            <hs:underlineShape val="solid"/>
+            <hs:underlineType val="1"/>
+            <hs:underlineColor rgb="ff1155cc"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff1155cc"/>
+            <x:u/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>휠체어석 이용 불편 후기</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve">
+</x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff1155cc"/>
+            <x:u/>
+            <hs:underlineShape val="solid"/>
+            <hs:underlineType val="1"/>
+            <hs:underlineColor rgb="ff1155cc"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff1155cc"/>
+            <x:u/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>휠체어 이용자 콘서트 관람 고민</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve">
+</x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff1155cc"/>
+            <x:u/>
+            <hs:underlineShape val="solid"/>
+            <hs:underlineType val="1"/>
+            <hs:underlineColor rgb="ff1155cc"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff1155cc"/>
+            <x:u/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>휠체어석 실태 기사</x:t>
+    </x:r>
   </x:si>
   <x:si>
     <x:t>이동권 문제: 콘서트장 주변에 인파가 몰려 수동 휠체어를 타고 이동하기 어려울까봐 두렵다. (감정)
 휠체어석은 무대쪽으로 고정되어 있어 아티스트가 이동하면 볼 수 없고, 다른 팬들이 일어서서 보게 되면 관람에 방해 받는다.</x:t>
   </x:si>
   <x:si>
-    <x:t>상영 중인  VR 콘서트를 찾아보니 휠체어석을 지원하지 않고 있어 VR 콘서트 감상 자체가 불가능하다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르소나가 직접 네이버 카페에 남긴 글을 근거로 pain point를 하나만 남김</x:t>
+    <x:t>수동휠체어를 타고 콘서트장에 가기 두렵고 휠체어석이 고정되어 있어 관람 제한을 받는 팬을 위해 서울에 있는 VR 상영관에서 콘서트 동시 상영을 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>롯데 시네마 홈페이지에서 직접 확인: 현재 상영 중인 엔하이픈의 VR 콘서트 경우 롯데시네마 홍대입구 상영관 휠체어석은 예매불가이며 월드타워점은 휠체어석이 없는 전체 소파석이라 휠체어 사용자는 예매 자체가 불가능함
+2026년 10월 7일 기준
+엔하이픈 브이알콘서트 : 데스티니
+롯데시네마 월드타워
+2026년 11월 1일까지 상영
+상영관은 10관 소파석 LASER로 전 좌석 소파석으로 휠체어석 자체가 없음
+롯데시네마 홍대입구
+2026년 11월 8일까지 상영
+상영관은 4관 LASER로 장애인석은 있으나 예매 활성화 안되어 있음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동권 문제와 휠체어 관람 제한 문제를 영화관 VR 상영으로 해결 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페르소나가 직접 네이버 카페에 남긴 글을 근거로 pain point를 하나만 남김
+(빈도X심각도를 기준으로 삼음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>★ v0 를 «지우지 않는다».  왼쪽에 어제 쓴 것을 그대로 옮겨 적고, 오른쪽에 오늘 고친 것을 쓴다.  그리고 ★ 맨 오른쪽 「왜 바꿨나」 한 줄이 이 양식의 전부다 —  이 한 줄이 수료 후 포트폴리오의  «D 고친 증거»가 된다.  ★ 안 바꾼 칸도 적는다.  «안 바꿨다 + 그 이유»는  «안 봤다»와 전혀 다르다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>① 공식 팬클럽 커뮤니에서 콘서트 정보를 알게됨 → ② 서울 VR 상영관 중 이동이 편리한 곳을 예매 → ③ 입장 전 굿즈 구매 → ④ 현장 입장, 동시 상영, 단체 응원 → ⑤ 공연 후기를 네이버 카페에 남김 → ★ 남는 것: 그날 구매한 굿즈와 티켓</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이머시브 콘텐츠를 할 근거가 없어서 이 기획안에서 이머시브 콘텐츠는 폐기함
+현재  VR 콘서트 상영 중인 극장에서 휠체어석을 제공하고 있지 않아 콘서트장에 직접 가는 선택지 밖에 없음, 링크된 기사처럼 장애인 이동을 위한 전담 스태프가 배치된 사례가 존재.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재  VR 콘서트 상영 중인 극장에서 휠체어석을 제공하고 있지 않아 콘서트장에 직접 가는 선택지 밖에 없음, 링크된 기사처럼 장애인 이동을 위한 전담 스태프가 배치된 사례가 존재.</x:t>
   </x:si>
   <x:si>
     <x:t>수동휠체어를 타고 콘서트장에 가기 두려운 지체장애인을 위해 전담 스태프를 배정한다.</x:t>
   </x:si>
   <x:si>
-    <x:t>v0  (어제 쓴 것 그대로)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현장 콘서트 티켓, 콘서트 굿즈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칸</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그대로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>①</x:t>
-  </x:si>
-  <x:si>
-    <x:t>★ 남은 «?» 개수  (어제 → 오늘)</x:t>
+    <x:t>⑥ 매출 · 운영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>★ v1  (오늘)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>④ 왜 이머시브인가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>★ 한 줄 요약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>티켓, 콘서트 굿즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세 개가 줄어듦</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실습 ② — v1 작성  (★ v0 와 나란히 두고)</x:t>
   </x:si>
   <x:si>
     <x:t>① 페르소나</x:t>
   </x:si>
   <x:si>
+    <x:t>1개(⑥)</x:t>
+  </x:si>
+  <x:si>
     <x:t>─ 정리 ─</x:t>
   </x:si>
   <x:si>
     <x:t>⑤ 경험 흐름</x:t>
   </x:si>
   <x:si>
-    <x:t>1개(⑥)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40대 초반 직장인, 서울 거주, 3년 전 사고로 복합장애를 얻어 수동휠체어를 사용, 한 아이돌 20년차 팬, 공식 팬클럽 가입, 음반/굿즈 수집, 장애를 얻기 전에는 콘서트, 팬미팅, 생일파티, 생일카페, 공개 방송과 같은 오프라인 스케줄에 자주 참여함. 장애인이 된 후로 오프라인 활동은 못하고 주말마다 스마트폰을 통해 공식 팬 커뮤니티, 네이버 카페로 소식을 얻고 팬활동을 함.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>③ 핵심 아이디어 한 줄</x:t>
-  </x:si>
-  <x:si>
-    <x:t>★ 왜 바꿨나 — 한 줄</x:t>
-  </x:si>
-  <x:si>
-    <x:t>② Pain Point</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페르소나가 구체적이라 생각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>★ 안 바꾼 칸 + 그 이유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>① 공식 팬클럽 커뮤니에서 콘서트 정보를 알게됨 → ② 서울 VR 상영관 중 이동이 편리한 곳을 예매 → ③ 입장 전 굿즈 구매 → ④ 현장 입장, 동시 상영, 단체 응원 → ⑤ 공연 후기를 네이버 카페에 남김 → ★ 남는 것: 그날 구매한 굿즈와 티켓</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수동휠체어를 타고 콘서트장에 가기 두렵고 휠체어석이 고정되어 있어 관람 제한을 받는 팬을 위해 서울에 있는 VR 상영관에서 콘서트 동시 상영을 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동권 문제: 콘서트장 주변에 인파가 몰려 수동 휠체어를 타고 이동하기 어려울까봐 두렵다. (감정)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>★ v0 를 «지우지 않는다».  왼쪽에 어제 쓴 것을 그대로 옮겨 적고, 오른쪽에 오늘 고친 것을 쓴다.  그리고 ★ 맨 오른쪽 「왜 바꿨나」 한 줄이 이 양식의 전부다 —  이 한 줄이 수료 후 포트폴리오의  «D 고친 증거»가 된다.  ★ 안 바꾼 칸도 적는다.  «안 바꿨다 + 그 이유»는  «안 봤다»와 전혀 다르다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>① 페르소나가 구체적이라 생각해서 바꾸지 않음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질문 카드 (막힌 점·헷갈리는 점 한 가지 이상)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동권 문제와 휠체어 관람 제한 문제를 영화관 VR 상영으로 해결 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.donga.com/news/Society/article/all/20260907/134619194/1</x:t>
-  </x:si>
-  <x:si>
     <x:t>휠체어 이용자의 이동권 보장을 위해 전담 스태프를 배치한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>K-POP 이머시브 콘텐츠 기획자 양성과정 · 1기   ·   17일차 W4-2 (금)   ·   STUDIO 1 · 막힘 진단 → 기획안 v1 (★ D 고친 증거)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재  VR 콘서트 상영 중인 극장에서 휠체어석을 제공하고 있지 않아 콘서트장에 직접 가는 선택지 밖에 없음, 링크된 기사처럼 장애인 이동을 위한 전담 스태프가 배치된 사례가 존재.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⑥ 매출 · 운영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>★ v1  (오늘)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>④ 왜 이머시브인가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>티켓, 콘서트 굿즈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>★ 한 줄 요약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세 개가 줄어듦</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실습 ② — v1 작성  (★ v0 와 나란히 두고)</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="14">
+  <x:fonts count="16">
     <x:font>
       <x:name val="Calibri"/>
       <x:sz val="11"/>
@@ -296,6 +422,36 @@
       <x:sz val="10"/>
       <x:color rgb="ff4a4a4a"/>
     </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff1155cc"/>
+          <x:u/>
+          <hs:underlineShape val="solid"/>
+          <hs:underlineType val="1"/>
+          <hs:underlineColor rgb="ff1155cc"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff1155cc"/>
+          <x:u/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -346,7 +502,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -393,7 +549,7 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -401,6 +557,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1013,12 +1172,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="14.199999999999999">
       <x:c r="A1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1" ht="20.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4" ht="33.75" customHeight="1">
@@ -1031,125 +1190,128 @@
     </x:row>
     <x:row r="4" spans="1:4" ht="33.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:4" ht="135" customHeight="1">
+    <x:row r="5" spans="1:5" ht="135" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>22</x:v>
+      <x:c r="E5" s="11" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4" ht="95.25" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="9" t="s">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5" ht="72.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5" ht="175.5" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B7" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5" ht="73.5" customHeight="1">
-      <x:c r="A8" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4" ht="114.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4" ht="81" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4" ht="78" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4" ht="21.75" customHeight="1">
       <x:c r="A12" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="8"/>
       <x:c r="C12" s="8"/>
@@ -1157,33 +1319,33 @@
     </x:row>
     <x:row r="13" spans="1:4" ht="51.75" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="9"/>
       <x:c r="D13" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4" ht="51.75" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:1" ht="14.199999999999999">
       <x:c r="A16" s="10" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4" ht="54" customHeight="1">
@@ -2177,7 +2339,8 @@
     <x:mergeCell ref="A17:D17"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink ref="E7:E7" r:id="rId1"/>
+    <x:hyperlink ref="E5:E5" r:id="rId1"/>
+    <x:hyperlink ref="E7:E7" r:id="rId2"/>
   </x:hyperlinks>
   <x:pageMargins left="0.30000001192092896" right="0.30000001192092896" top="0.40000000596046448" bottom="0.40000000596046448" header="0" footer="0"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
